--- a/lab-standards/DTE-lab-standard.xlsx
+++ b/lab-standards/DTE-lab-standard.xlsx
@@ -565,6 +565,10 @@
           <t>SICIP required space for 25 trainees</t>
         </is>
       </c>
+      <c r="D7" s="11" t="n"/>
+      <c r="E7" s="11" t="n"/>
+      <c r="F7" s="11" t="n"/>
+      <c r="G7" s="12" t="n"/>
     </row>
     <row r="8" ht="52.2" customHeight="1">
       <c r="B8" s="2" t="inlineStr">
@@ -579,6 +583,10 @@
 Classroom cum workshop – 1000 sft (93 sqm)</t>
         </is>
       </c>
+      <c r="D8" s="11" t="n"/>
+      <c r="E8" s="11" t="n"/>
+      <c r="F8" s="11" t="n"/>
+      <c r="G8" s="12" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -648,7 +656,9 @@
       <c r="C16" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D16" s="9" t="n"/>
+      <c r="D16" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E16" s="9" t="n">
         <v>5</v>
       </c>
@@ -670,7 +680,9 @@
       <c r="C17" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D17" s="9" t="n"/>
+      <c r="D17" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E17" s="9" t="n">
         <v>5</v>
       </c>
@@ -692,7 +704,9 @@
       <c r="C18" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D18" s="9" t="n"/>
+      <c r="D18" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E18" s="9" t="n">
         <v>5</v>
       </c>
@@ -714,7 +728,9 @@
       <c r="C19" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D19" s="9" t="n"/>
+      <c r="D19" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E19" s="9" t="n">
         <v>9</v>
       </c>
@@ -736,7 +752,9 @@
       <c r="C20" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="D20" s="9" t="n"/>
+      <c r="D20" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E20" s="9" t="n">
         <v>8</v>
       </c>
@@ -758,7 +776,9 @@
       <c r="C21" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D21" s="9" t="n"/>
+      <c r="D21" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E21" s="9" t="n">
         <v>9</v>
       </c>
@@ -780,7 +800,9 @@
       <c r="C22" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D22" s="9" t="n"/>
+      <c r="D22" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E22" s="9" t="n">
         <v>9</v>
       </c>
@@ -802,7 +824,9 @@
       <c r="C23" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D23" s="9" t="n"/>
+      <c r="D23" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E23" s="9" t="n">
         <v>8</v>
       </c>
@@ -824,7 +848,9 @@
       <c r="C24" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D24" s="9" t="n"/>
+      <c r="D24" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E24" s="9" t="n">
         <v>6</v>
       </c>
@@ -846,7 +872,9 @@
       <c r="C25" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D25" s="9" t="n"/>
+      <c r="D25" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E25" s="9" t="n">
         <v>6</v>
       </c>
@@ -868,7 +896,9 @@
       <c r="C26" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="D26" s="9" t="n"/>
+      <c r="D26" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E26" s="9" t="n">
         <v>6</v>
       </c>
@@ -890,7 +920,9 @@
       <c r="C27" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D27" s="9" t="n"/>
+      <c r="D27" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E27" s="9" t="n">
         <v>5</v>
       </c>
@@ -912,7 +944,9 @@
       <c r="C28" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D28" s="9" t="n"/>
+      <c r="D28" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E28" s="9" t="n">
         <v>5</v>
       </c>
@@ -934,7 +968,9 @@
       <c r="C29" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="D29" s="9" t="n"/>
+      <c r="D29" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E29" s="9" t="n">
         <v>4</v>
       </c>
@@ -956,7 +992,9 @@
       <c r="C30" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D30" s="9" t="n"/>
+      <c r="D30" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E30" s="9" t="n">
         <v>7</v>
       </c>
@@ -978,7 +1016,9 @@
       <c r="C31" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="D31" s="9" t="n"/>
+      <c r="D31" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E31" s="9" t="n">
         <v>3</v>
       </c>
@@ -1124,6 +1164,10 @@
           <t>SICIP required space for 25 trainees</t>
         </is>
       </c>
+      <c r="D7" s="11" t="n"/>
+      <c r="E7" s="11" t="n"/>
+      <c r="F7" s="11" t="n"/>
+      <c r="G7" s="12" t="n"/>
     </row>
     <row r="8" ht="52.2" customHeight="1">
       <c r="B8" s="2" t="inlineStr">
@@ -1138,6 +1182,10 @@
 Classroom cum workshop – 1000 sft (93 sqm)</t>
         </is>
       </c>
+      <c r="D8" s="11" t="n"/>
+      <c r="E8" s="11" t="n"/>
+      <c r="F8" s="11" t="n"/>
+      <c r="G8" s="12" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -1207,7 +1255,9 @@
       <c r="C16" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D16" s="9" t="n"/>
+      <c r="D16" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E16" s="9" t="n">
         <v>5</v>
       </c>
@@ -1229,7 +1279,9 @@
       <c r="C17" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D17" s="9" t="n"/>
+      <c r="D17" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E17" s="9" t="n">
         <v>5</v>
       </c>
@@ -1251,7 +1303,9 @@
       <c r="C18" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D18" s="9" t="n"/>
+      <c r="D18" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E18" s="9" t="n">
         <v>9</v>
       </c>
@@ -1273,7 +1327,9 @@
       <c r="C19" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D19" s="9" t="n"/>
+      <c r="D19" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E19" s="9" t="n">
         <v>6</v>
       </c>
@@ -1295,7 +1351,9 @@
       <c r="C20" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D20" s="9" t="n"/>
+      <c r="D20" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E20" s="9" t="n">
         <v>6</v>
       </c>
@@ -1317,7 +1375,9 @@
       <c r="C21" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D21" s="9" t="n"/>
+      <c r="D21" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E21" s="9" t="n">
         <v>6</v>
       </c>
@@ -1339,7 +1399,9 @@
       <c r="C22" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D22" s="9" t="n"/>
+      <c r="D22" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E22" s="9" t="n">
         <v>6</v>
       </c>
@@ -1361,7 +1423,9 @@
       <c r="C23" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D23" s="9" t="n"/>
+      <c r="D23" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E23" s="9" t="n">
         <v>5</v>
       </c>
@@ -1383,7 +1447,9 @@
       <c r="C24" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D24" s="9" t="n"/>
+      <c r="D24" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E24" s="9" t="n">
         <v>5</v>
       </c>
@@ -1405,7 +1471,9 @@
       <c r="C25" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D25" s="9" t="n"/>
+      <c r="D25" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E25" s="9" t="n">
         <v>5</v>
       </c>
@@ -1427,7 +1495,9 @@
       <c r="C26" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D26" s="9" t="n"/>
+      <c r="D26" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E26" s="9" t="n">
         <v>5</v>
       </c>
@@ -1449,7 +1519,9 @@
       <c r="C27" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D27" s="9" t="n"/>
+      <c r="D27" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E27" s="9" t="n">
         <v>4</v>
       </c>
@@ -1471,7 +1543,9 @@
       <c r="C28" s="9" t="n">
         <v>16</v>
       </c>
-      <c r="D28" s="9" t="n"/>
+      <c r="D28" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E28" s="9" t="n">
         <v>8</v>
       </c>
@@ -1493,7 +1567,9 @@
       <c r="C29" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D29" s="9" t="n"/>
+      <c r="D29" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E29" s="9" t="n">
         <v>8</v>
       </c>
@@ -1515,7 +1591,9 @@
       <c r="C30" s="9" t="n">
         <v>16</v>
       </c>
-      <c r="D30" s="9" t="n"/>
+      <c r="D30" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E30" s="9" t="n">
         <v>6</v>
       </c>
@@ -1537,7 +1615,9 @@
       <c r="C31" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D31" s="9" t="n"/>
+      <c r="D31" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E31" s="9" t="n">
         <v>6</v>
       </c>
@@ -1559,7 +1639,9 @@
       <c r="C32" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D32" s="9" t="n"/>
+      <c r="D32" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E32" s="9" t="n">
         <v>6</v>
       </c>
@@ -1581,7 +1663,9 @@
       <c r="C33" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D33" s="9" t="n"/>
+      <c r="D33" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E33" s="9" t="n">
         <v>6</v>
       </c>
@@ -1603,7 +1687,9 @@
       <c r="C34" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D34" s="9" t="n"/>
+      <c r="D34" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E34" s="9" t="n">
         <v>8</v>
       </c>
@@ -1625,7 +1711,9 @@
       <c r="C35" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D35" s="9" t="n"/>
+      <c r="D35" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E35" s="9" t="n">
         <v>7</v>
       </c>
@@ -1647,7 +1735,9 @@
       <c r="C36" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D36" s="9" t="n"/>
+      <c r="D36" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E36" s="9" t="n">
         <v>5</v>
       </c>
@@ -1669,7 +1759,9 @@
       <c r="C37" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D37" s="9" t="n"/>
+      <c r="D37" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E37" s="9" t="n">
         <v>6</v>
       </c>
@@ -1691,7 +1783,9 @@
       <c r="C38" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D38" s="9" t="n"/>
+      <c r="D38" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E38" s="9" t="n">
         <v>5</v>
       </c>
@@ -1837,6 +1931,10 @@
           <t>SICIP required space for 25 trainees</t>
         </is>
       </c>
+      <c r="D7" s="11" t="n"/>
+      <c r="E7" s="11" t="n"/>
+      <c r="F7" s="11" t="n"/>
+      <c r="G7" s="12" t="n"/>
     </row>
     <row r="8" ht="52.2" customHeight="1">
       <c r="B8" s="2" t="inlineStr">
@@ -1852,6 +1950,10 @@
 Classroom cum workshop – 1000 sft (93 sqm)</t>
         </is>
       </c>
+      <c r="D8" s="11" t="n"/>
+      <c r="E8" s="11" t="n"/>
+      <c r="F8" s="11" t="n"/>
+      <c r="G8" s="12" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -1921,7 +2023,9 @@
       <c r="C16" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D16" s="9" t="n"/>
+      <c r="D16" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E16" s="9" t="n">
         <v>5</v>
       </c>
@@ -1943,7 +2047,9 @@
       <c r="C17" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D17" s="9" t="n"/>
+      <c r="D17" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E17" s="9" t="n">
         <v>5</v>
       </c>
@@ -1965,7 +2071,9 @@
       <c r="C18" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="D18" s="9" t="n"/>
+      <c r="D18" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E18" s="9" t="n">
         <v>10</v>
       </c>
@@ -1987,7 +2095,9 @@
       <c r="C19" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D19" s="9" t="n"/>
+      <c r="D19" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E19" s="9" t="n">
         <v>8</v>
       </c>
@@ -2009,7 +2119,9 @@
       <c r="C20" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D20" s="9" t="n"/>
+      <c r="D20" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E20" s="9" t="n">
         <v>8</v>
       </c>
@@ -2031,7 +2143,9 @@
       <c r="C21" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D21" s="9" t="n"/>
+      <c r="D21" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E21" s="9" t="n">
         <v>6</v>
       </c>
@@ -2053,7 +2167,9 @@
       <c r="C22" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D22" s="9" t="n"/>
+      <c r="D22" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E22" s="9" t="n">
         <v>6</v>
       </c>
@@ -2075,7 +2191,9 @@
       <c r="C23" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D23" s="9" t="n"/>
+      <c r="D23" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E23" s="9" t="n">
         <v>5</v>
       </c>
@@ -2097,7 +2215,9 @@
       <c r="C24" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D24" s="9" t="n"/>
+      <c r="D24" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E24" s="9" t="n">
         <v>5</v>
       </c>
@@ -2119,7 +2239,9 @@
       <c r="C25" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D25" s="9" t="n"/>
+      <c r="D25" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E25" s="9" t="n">
         <v>5</v>
       </c>
@@ -2265,6 +2387,10 @@
           <t>SICIP required space for 25 trainees</t>
         </is>
       </c>
+      <c r="D7" s="11" t="n"/>
+      <c r="E7" s="11" t="n"/>
+      <c r="F7" s="11" t="n"/>
+      <c r="G7" s="12" t="n"/>
     </row>
     <row r="8" ht="52.2" customHeight="1">
       <c r="B8" s="2" t="inlineStr">
@@ -2279,6 +2405,10 @@
 Classroom cum workshop – 1000 sft (93 sqm)</t>
         </is>
       </c>
+      <c r="D8" s="11" t="n"/>
+      <c r="E8" s="11" t="n"/>
+      <c r="F8" s="11" t="n"/>
+      <c r="G8" s="12" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -2348,7 +2478,9 @@
       <c r="C16" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D16" s="9" t="n"/>
+      <c r="D16" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E16" s="9" t="n">
         <v>5</v>
       </c>
@@ -2370,7 +2502,9 @@
       <c r="C17" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D17" s="9" t="n"/>
+      <c r="D17" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E17" s="9" t="n">
         <v>5</v>
       </c>
@@ -2392,7 +2526,9 @@
       <c r="C18" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D18" s="9" t="n"/>
+      <c r="D18" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E18" s="9" t="n">
         <v>5</v>
       </c>
@@ -2414,7 +2550,9 @@
       <c r="C19" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D19" s="9" t="n"/>
+      <c r="D19" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E19" s="9" t="n">
         <v>9</v>
       </c>
@@ -2436,7 +2574,9 @@
       <c r="C20" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="D20" s="9" t="n"/>
+      <c r="D20" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E20" s="9" t="n">
         <v>8</v>
       </c>
@@ -2458,7 +2598,9 @@
       <c r="C21" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D21" s="9" t="n"/>
+      <c r="D21" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E21" s="9" t="n">
         <v>9</v>
       </c>
@@ -2480,7 +2622,9 @@
       <c r="C22" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D22" s="9" t="n"/>
+      <c r="D22" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E22" s="9" t="n">
         <v>9</v>
       </c>
@@ -2502,7 +2646,9 @@
       <c r="C23" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="D23" s="9" t="n"/>
+      <c r="D23" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E23" s="9" t="n">
         <v>8</v>
       </c>
@@ -2524,7 +2670,9 @@
       <c r="C24" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D24" s="9" t="n"/>
+      <c r="D24" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E24" s="9" t="n">
         <v>6</v>
       </c>
@@ -2546,7 +2694,9 @@
       <c r="C25" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D25" s="9" t="n"/>
+      <c r="D25" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E25" s="9" t="n">
         <v>6</v>
       </c>
@@ -2568,7 +2718,9 @@
       <c r="C26" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D26" s="9" t="n"/>
+      <c r="D26" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E26" s="9" t="n">
         <v>6</v>
       </c>
@@ -2590,7 +2742,9 @@
       <c r="C27" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D27" s="9" t="n"/>
+      <c r="D27" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E27" s="9" t="n">
         <v>5</v>
       </c>
@@ -2612,7 +2766,9 @@
       <c r="C28" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D28" s="9" t="n"/>
+      <c r="D28" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E28" s="9" t="n">
         <v>5</v>
       </c>
@@ -2634,7 +2790,9 @@
       <c r="C29" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="D29" s="9" t="n"/>
+      <c r="D29" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E29" s="9" t="n">
         <v>4</v>
       </c>
@@ -2656,7 +2814,9 @@
       <c r="C30" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D30" s="9" t="n"/>
+      <c r="D30" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E30" s="9" t="n">
         <v>7</v>
       </c>
@@ -2678,7 +2838,9 @@
       <c r="C31" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="D31" s="9" t="n"/>
+      <c r="D31" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E31" s="9" t="n">
         <v>3</v>
       </c>
@@ -2824,6 +2986,10 @@
           <t>SICIP required space for 30 trainees</t>
         </is>
       </c>
+      <c r="D7" s="11" t="n"/>
+      <c r="E7" s="11" t="n"/>
+      <c r="F7" s="11" t="n"/>
+      <c r="G7" s="12" t="n"/>
     </row>
     <row r="8" ht="52.2" customHeight="1">
       <c r="B8" s="2" t="inlineStr">
@@ -2839,6 +3005,10 @@
 Classroom cum workshop – 1000 sft (93 sqm)</t>
         </is>
       </c>
+      <c r="D8" s="11" t="n"/>
+      <c r="E8" s="11" t="n"/>
+      <c r="F8" s="11" t="n"/>
+      <c r="G8" s="12" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -2908,7 +3078,9 @@
       <c r="C16" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D16" s="9" t="n"/>
+      <c r="D16" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E16" s="9" t="n">
         <v>5</v>
       </c>
@@ -2930,7 +3102,9 @@
       <c r="C17" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D17" s="9" t="n"/>
+      <c r="D17" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E17" s="9" t="n">
         <v>5</v>
       </c>
@@ -2952,7 +3126,9 @@
       <c r="C18" s="9" t="n">
         <v>30</v>
       </c>
-      <c r="D18" s="9" t="n"/>
+      <c r="D18" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E18" s="9" t="n">
         <v>10</v>
       </c>
@@ -2974,7 +3150,9 @@
       <c r="C19" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D19" s="9" t="n"/>
+      <c r="D19" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E19" s="9" t="n">
         <v>8</v>
       </c>
@@ -2996,7 +3174,9 @@
       <c r="C20" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D20" s="9" t="n"/>
+      <c r="D20" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E20" s="9" t="n">
         <v>8</v>
       </c>
@@ -3018,7 +3198,9 @@
       <c r="C21" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D21" s="9" t="n"/>
+      <c r="D21" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E21" s="9" t="n">
         <v>8</v>
       </c>
@@ -3040,7 +3222,9 @@
       <c r="C22" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D22" s="9" t="n"/>
+      <c r="D22" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E22" s="9" t="n">
         <v>7</v>
       </c>
@@ -3062,7 +3246,9 @@
       <c r="C23" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="D23" s="9" t="n"/>
+      <c r="D23" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E23" s="9" t="n">
         <v>7</v>
       </c>
@@ -3084,7 +3270,9 @@
       <c r="C24" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D24" s="9" t="n"/>
+      <c r="D24" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E24" s="9" t="n">
         <v>7</v>
       </c>
@@ -3106,7 +3294,9 @@
       <c r="C25" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D25" s="9" t="n"/>
+      <c r="D25" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E25" s="9" t="n">
         <v>7</v>
       </c>
@@ -3128,7 +3318,9 @@
       <c r="C26" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D26" s="9" t="n"/>
+      <c r="D26" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E26" s="9" t="n">
         <v>8</v>
       </c>
@@ -3150,7 +3342,9 @@
       <c r="C27" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D27" s="9" t="n"/>
+      <c r="D27" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E27" s="9" t="n">
         <v>5</v>
       </c>
@@ -3172,7 +3366,9 @@
       <c r="C28" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D28" s="9" t="n"/>
+      <c r="D28" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E28" s="9" t="n">
         <v>5</v>
       </c>
@@ -3194,7 +3390,9 @@
       <c r="C29" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D29" s="9" t="n"/>
+      <c r="D29" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E29" s="9" t="n">
         <v>5</v>
       </c>
@@ -3340,6 +3538,10 @@
           <t>SICIP required space for 25 trainees</t>
         </is>
       </c>
+      <c r="D7" s="11" t="n"/>
+      <c r="E7" s="11" t="n"/>
+      <c r="F7" s="11" t="n"/>
+      <c r="G7" s="12" t="n"/>
     </row>
     <row r="8" ht="52.2" customHeight="1">
       <c r="B8" s="2" t="inlineStr">
@@ -3354,6 +3556,10 @@
 Classroom cum workshop – 1000 sft (93 sqm)</t>
         </is>
       </c>
+      <c r="D8" s="11" t="n"/>
+      <c r="E8" s="11" t="n"/>
+      <c r="F8" s="11" t="n"/>
+      <c r="G8" s="12" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -3423,7 +3629,9 @@
       <c r="C16" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D16" s="9" t="n"/>
+      <c r="D16" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E16" s="9" t="n">
         <v>5</v>
       </c>
@@ -3445,7 +3653,9 @@
       <c r="C17" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D17" s="9" t="n"/>
+      <c r="D17" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E17" s="9" t="n">
         <v>5</v>
       </c>
@@ -3467,7 +3677,9 @@
       <c r="C18" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="D18" s="9" t="n"/>
+      <c r="D18" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E18" s="9" t="n">
         <v>9</v>
       </c>
@@ -3489,7 +3701,9 @@
       <c r="C19" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D19" s="9" t="n"/>
+      <c r="D19" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E19" s="9" t="n">
         <v>8</v>
       </c>
@@ -3511,7 +3725,9 @@
       <c r="C20" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D20" s="9" t="n"/>
+      <c r="D20" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E20" s="9" t="n">
         <v>8</v>
       </c>
@@ -3533,7 +3749,9 @@
       <c r="C21" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D21" s="9" t="n"/>
+      <c r="D21" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E21" s="9" t="n">
         <v>8</v>
       </c>
@@ -3555,7 +3773,9 @@
       <c r="C22" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D22" s="9" t="n"/>
+      <c r="D22" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E22" s="9" t="n">
         <v>7</v>
       </c>
@@ -3577,7 +3797,9 @@
       <c r="C23" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D23" s="9" t="n"/>
+      <c r="D23" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E23" s="9" t="n">
         <v>7</v>
       </c>
@@ -3599,7 +3821,9 @@
       <c r="C24" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="D24" s="9" t="n"/>
+      <c r="D24" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E24" s="9" t="n">
         <v>6</v>
       </c>
@@ -3621,7 +3845,9 @@
       <c r="C25" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="D25" s="9" t="n"/>
+      <c r="D25" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E25" s="9" t="n">
         <v>6</v>
       </c>
@@ -3643,7 +3869,9 @@
       <c r="C26" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D26" s="9" t="n"/>
+      <c r="D26" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E26" s="9" t="n">
         <v>7</v>
       </c>
@@ -3665,7 +3893,9 @@
       <c r="C27" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D27" s="9" t="n"/>
+      <c r="D27" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E27" s="9" t="n">
         <v>6</v>
       </c>
@@ -3687,7 +3917,9 @@
       <c r="C28" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D28" s="9" t="n"/>
+      <c r="D28" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E28" s="9" t="n">
         <v>6</v>
       </c>
@@ -3709,7 +3941,9 @@
       <c r="C29" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D29" s="9" t="n"/>
+      <c r="D29" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E29" s="9" t="n">
         <v>6</v>
       </c>
@@ -3731,7 +3965,9 @@
       <c r="C30" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D30" s="9" t="n"/>
+      <c r="D30" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E30" s="9" t="n">
         <v>6</v>
       </c>
@@ -3753,7 +3989,9 @@
       <c r="C31" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D31" s="9" t="n"/>
+      <c r="D31" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E31" s="9" t="n">
         <v>5</v>
       </c>
@@ -3775,7 +4013,9 @@
       <c r="C32" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D32" s="9" t="n"/>
+      <c r="D32" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E32" s="9" t="n">
         <v>5</v>
       </c>
@@ -3797,7 +4037,9 @@
       <c r="C33" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D33" s="9" t="n"/>
+      <c r="D33" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E33" s="9" t="n">
         <v>5</v>
       </c>
@@ -3819,7 +4061,9 @@
       <c r="C34" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D34" s="9" t="n"/>
+      <c r="D34" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E34" s="9" t="n">
         <v>6</v>
       </c>
@@ -3841,7 +4085,9 @@
       <c r="C35" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="D35" s="9" t="n"/>
+      <c r="D35" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E35" s="9" t="n">
         <v>6</v>
       </c>
@@ -3863,7 +4109,9 @@
       <c r="C36" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D36" s="9" t="n"/>
+      <c r="D36" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E36" s="9" t="n">
         <v>4</v>
       </c>
@@ -3885,7 +4133,9 @@
       <c r="C37" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D37" s="9" t="n"/>
+      <c r="D37" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E37" s="9" t="n">
         <v>5</v>
       </c>
@@ -3907,7 +4157,9 @@
       <c r="C38" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D38" s="9" t="n"/>
+      <c r="D38" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E38" s="9" t="n">
         <v>4</v>
       </c>
@@ -4053,6 +4305,10 @@
           <t>SICIP required space for 25 trainees</t>
         </is>
       </c>
+      <c r="D7" s="11" t="n"/>
+      <c r="E7" s="11" t="n"/>
+      <c r="F7" s="11" t="n"/>
+      <c r="G7" s="12" t="n"/>
     </row>
     <row r="8" ht="52.2" customHeight="1">
       <c r="B8" s="2" t="inlineStr">
@@ -4067,6 +4323,10 @@
 Classroom cum workshop – 1000 sft (93 sqm)</t>
         </is>
       </c>
+      <c r="D8" s="11" t="n"/>
+      <c r="E8" s="11" t="n"/>
+      <c r="F8" s="11" t="n"/>
+      <c r="G8" s="12" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -4136,7 +4396,9 @@
       <c r="C16" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D16" s="9" t="n"/>
+      <c r="D16" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E16" s="9" t="n">
         <v>5</v>
       </c>
@@ -4158,7 +4420,9 @@
       <c r="C17" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D17" s="9" t="n"/>
+      <c r="D17" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E17" s="9" t="n">
         <v>5</v>
       </c>
@@ -4180,7 +4444,9 @@
       <c r="C18" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D18" s="9" t="n"/>
+      <c r="D18" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E18" s="9" t="n">
         <v>5</v>
       </c>
@@ -4202,7 +4468,9 @@
       <c r="C19" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D19" s="9" t="n"/>
+      <c r="D19" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E19" s="9" t="n">
         <v>5</v>
       </c>
@@ -4224,7 +4492,9 @@
       <c r="C20" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D20" s="9" t="n"/>
+      <c r="D20" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E20" s="9" t="n">
         <v>4</v>
       </c>
@@ -4246,7 +4516,9 @@
       <c r="C21" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D21" s="9" t="n"/>
+      <c r="D21" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E21" s="9" t="n">
         <v>4</v>
       </c>
@@ -4268,7 +4540,9 @@
       <c r="C22" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="D22" s="9" t="n"/>
+      <c r="D22" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E22" s="9" t="n">
         <v>7</v>
       </c>
@@ -4290,7 +4564,9 @@
       <c r="C23" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D23" s="9" t="n"/>
+      <c r="D23" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E23" s="9" t="n">
         <v>7</v>
       </c>
@@ -4312,7 +4588,9 @@
       <c r="C24" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D24" s="9" t="n"/>
+      <c r="D24" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E24" s="9" t="n">
         <v>4</v>
       </c>
@@ -4334,7 +4612,9 @@
       <c r="C25" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D25" s="9" t="n"/>
+      <c r="D25" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E25" s="9" t="n">
         <v>4</v>
       </c>
@@ -4356,7 +4636,9 @@
       <c r="C26" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D26" s="9" t="n"/>
+      <c r="D26" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E26" s="9" t="n">
         <v>4</v>
       </c>
@@ -4378,7 +4660,9 @@
       <c r="C27" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D27" s="9" t="n"/>
+      <c r="D27" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E27" s="9" t="n">
         <v>5</v>
       </c>
@@ -4524,6 +4808,10 @@
           <t>SICIP required space for 25 trainees</t>
         </is>
       </c>
+      <c r="D7" s="11" t="n"/>
+      <c r="E7" s="11" t="n"/>
+      <c r="F7" s="11" t="n"/>
+      <c r="G7" s="12" t="n"/>
     </row>
     <row r="8" ht="52.2" customHeight="1">
       <c r="B8" s="2" t="inlineStr">
@@ -4539,6 +4827,10 @@
 Classroom cum workshop – 1000 sft (93 sqm)</t>
         </is>
       </c>
+      <c r="D8" s="11" t="n"/>
+      <c r="E8" s="11" t="n"/>
+      <c r="F8" s="11" t="n"/>
+      <c r="G8" s="12" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -4608,7 +4900,9 @@
       <c r="C16" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D16" s="9" t="n"/>
+      <c r="D16" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E16" s="9" t="n">
         <v>8</v>
       </c>
@@ -4630,7 +4924,9 @@
       <c r="C17" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D17" s="9" t="n"/>
+      <c r="D17" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E17" s="9" t="n">
         <v>6</v>
       </c>
@@ -4652,7 +4948,9 @@
       <c r="C18" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D18" s="9" t="n"/>
+      <c r="D18" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E18" s="9" t="n">
         <v>6</v>
       </c>
@@ -4675,7 +4973,9 @@
       <c r="C19" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="D19" s="9" t="n"/>
+      <c r="D19" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E19" s="9" t="n">
         <v>10</v>
       </c>
@@ -4698,7 +4998,9 @@
       <c r="C20" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D20" s="9" t="n"/>
+      <c r="D20" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E20" s="9" t="n">
         <v>6</v>
       </c>
@@ -4720,7 +5022,9 @@
       <c r="C21" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D21" s="9" t="n"/>
+      <c r="D21" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E21" s="9" t="n">
         <v>9</v>
       </c>
@@ -4746,7 +5050,9 @@
       <c r="C22" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D22" s="9" t="n"/>
+      <c r="D22" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E22" s="9" t="n">
         <v>8</v>
       </c>
@@ -4772,7 +5078,9 @@
       <c r="C23" s="9" t="n">
         <v>100</v>
       </c>
-      <c r="D23" s="9" t="n"/>
+      <c r="D23" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E23" s="9" t="n">
         <v>7</v>
       </c>
@@ -4798,7 +5106,9 @@
       <c r="C24" s="9" t="n">
         <v>100</v>
       </c>
-      <c r="D24" s="9" t="n"/>
+      <c r="D24" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E24" s="9" t="n">
         <v>4</v>
       </c>
@@ -4820,7 +5130,9 @@
       <c r="C25" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="D25" s="9" t="n"/>
+      <c r="D25" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E25" s="9" t="n">
         <v>3</v>
       </c>
@@ -4842,7 +5154,9 @@
       <c r="C26" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D26" s="9" t="n"/>
+      <c r="D26" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E26" s="9" t="n">
         <v>7</v>
       </c>
@@ -4864,7 +5178,9 @@
       <c r="C27" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="D27" s="9" t="n"/>
+      <c r="D27" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E27" s="9" t="n">
         <v>8</v>
       </c>
@@ -4886,7 +5202,9 @@
       <c r="C28" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="D28" s="9" t="n"/>
+      <c r="D28" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E28" s="9" t="n">
         <v>8</v>
       </c>
@@ -4908,7 +5226,9 @@
       <c r="C29" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="D29" s="9" t="n"/>
+      <c r="D29" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E29" s="9" t="n">
         <v>7</v>
       </c>
@@ -4930,7 +5250,9 @@
       <c r="C30" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="D30" s="9" t="n"/>
+      <c r="D30" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E30" s="9" t="n">
         <v>8</v>
       </c>
@@ -4952,7 +5274,9 @@
       <c r="C31" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="D31" s="9" t="n"/>
+      <c r="D31" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E31" s="9" t="n">
         <v>7</v>
       </c>
@@ -4974,7 +5298,9 @@
       <c r="C32" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D32" s="9" t="n"/>
+      <c r="D32" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E32" s="9" t="n">
         <v>6</v>
       </c>
@@ -4996,7 +5322,9 @@
       <c r="C33" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D33" s="9" t="n"/>
+      <c r="D33" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E33" s="9" t="n">
         <v>6</v>
       </c>
@@ -5018,7 +5346,9 @@
       <c r="C34" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D34" s="9" t="n"/>
+      <c r="D34" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E34" s="9" t="n">
         <v>5</v>
       </c>
@@ -5040,7 +5370,9 @@
       <c r="C35" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="D35" s="9" t="n"/>
+      <c r="D35" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E35" s="9" t="n">
         <v>4</v>
       </c>
@@ -5062,7 +5394,9 @@
       <c r="C36" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="D36" s="9" t="n"/>
+      <c r="D36" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E36" s="9" t="n">
         <v>3</v>
       </c>
@@ -5084,7 +5418,9 @@
       <c r="C37" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="D37" s="9" t="n"/>
+      <c r="D37" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E37" s="9" t="n">
         <v>3</v>
       </c>
@@ -5106,7 +5442,9 @@
       <c r="C38" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="D38" s="9" t="n"/>
+      <c r="D38" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E38" s="9" t="n">
         <v>3</v>
       </c>
@@ -5128,7 +5466,9 @@
       <c r="C39" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="D39" s="9" t="n"/>
+      <c r="D39" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E39" s="9" t="n">
         <v>4</v>
       </c>
@@ -5150,7 +5490,9 @@
       <c r="C40" s="9" t="n">
         <v>15</v>
       </c>
-      <c r="D40" s="9" t="n"/>
+      <c r="D40" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E40" s="9" t="n">
         <v>8</v>
       </c>
@@ -5172,7 +5514,9 @@
       <c r="C41" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D41" s="9" t="n"/>
+      <c r="D41" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E41" s="9" t="n">
         <v>7</v>
       </c>
@@ -5244,8 +5588,8 @@
     <mergeCell ref="C7:G7"/>
     <mergeCell ref="A44:G44"/>
     <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A43:E43"/>
     <mergeCell ref="A42:D42"/>
-    <mergeCell ref="A43:E43"/>
     <mergeCell ref="A45:E45"/>
     <mergeCell ref="C8:G8"/>
   </mergeCells>
@@ -5318,6 +5662,10 @@
           <t>SICIP required space for 25 trainees</t>
         </is>
       </c>
+      <c r="D7" s="11" t="n"/>
+      <c r="E7" s="11" t="n"/>
+      <c r="F7" s="11" t="n"/>
+      <c r="G7" s="12" t="n"/>
     </row>
     <row r="8" ht="52.2" customHeight="1">
       <c r="B8" s="2" t="inlineStr">
@@ -5333,6 +5681,10 @@
 Classroom cum workshop – 1000 sft (93 sqm)</t>
         </is>
       </c>
+      <c r="D8" s="11" t="n"/>
+      <c r="E8" s="11" t="n"/>
+      <c r="F8" s="11" t="n"/>
+      <c r="G8" s="12" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -5402,7 +5754,9 @@
       <c r="C16" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D16" s="9" t="n"/>
+      <c r="D16" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E16" s="9" t="n">
         <v>5</v>
       </c>
@@ -5424,7 +5778,9 @@
       <c r="C17" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D17" s="9" t="n"/>
+      <c r="D17" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E17" s="9" t="n">
         <v>5</v>
       </c>
@@ -5446,7 +5802,9 @@
       <c r="C18" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D18" s="9" t="n"/>
+      <c r="D18" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E18" s="9" t="n">
         <v>4</v>
       </c>
@@ -5468,7 +5826,9 @@
       <c r="C19" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="D19" s="9" t="n"/>
+      <c r="D19" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E19" s="9" t="n">
         <v>9</v>
       </c>
@@ -5490,7 +5850,9 @@
       <c r="C20" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D20" s="9" t="n"/>
+      <c r="D20" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E20" s="9" t="n">
         <v>7</v>
       </c>
@@ -5512,7 +5874,9 @@
       <c r="C21" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="D21" s="9" t="n"/>
+      <c r="D21" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E21" s="9" t="n">
         <v>6</v>
       </c>
@@ -5534,7 +5898,9 @@
       <c r="C22" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D22" s="9" t="n"/>
+      <c r="D22" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E22" s="9" t="n">
         <v>7</v>
       </c>
@@ -5556,7 +5922,9 @@
       <c r="C23" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D23" s="9" t="n"/>
+      <c r="D23" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E23" s="9" t="n">
         <v>5</v>
       </c>
@@ -5578,7 +5946,9 @@
       <c r="C24" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="D24" s="9" t="n"/>
+      <c r="D24" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E24" s="9" t="n">
         <v>4</v>
       </c>
@@ -5600,7 +5970,9 @@
       <c r="C25" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="D25" s="9" t="n"/>
+      <c r="D25" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E25" s="9" t="n">
         <v>4</v>
       </c>
@@ -5622,7 +5994,9 @@
       <c r="C26" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="D26" s="9" t="n"/>
+      <c r="D26" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E26" s="9" t="n">
         <v>3</v>
       </c>
@@ -5768,6 +6142,10 @@
           <t>SICIP required space for 25 trainees</t>
         </is>
       </c>
+      <c r="D7" s="11" t="n"/>
+      <c r="E7" s="11" t="n"/>
+      <c r="F7" s="11" t="n"/>
+      <c r="G7" s="12" t="n"/>
     </row>
     <row r="8" ht="52.2" customHeight="1">
       <c r="B8" s="2" t="inlineStr">
@@ -5782,6 +6160,10 @@
 Classroom cum workshop – 1000 sft (93 sqm)</t>
         </is>
       </c>
+      <c r="D8" s="11" t="n"/>
+      <c r="E8" s="11" t="n"/>
+      <c r="F8" s="11" t="n"/>
+      <c r="G8" s="12" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -5851,7 +6233,9 @@
       <c r="C16" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D16" s="9" t="n"/>
+      <c r="D16" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E16" s="9" t="n">
         <v>5</v>
       </c>
@@ -5873,7 +6257,9 @@
       <c r="C17" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D17" s="9" t="n"/>
+      <c r="D17" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E17" s="9" t="n">
         <v>5</v>
       </c>
@@ -5895,7 +6281,9 @@
       <c r="C18" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D18" s="9" t="n"/>
+      <c r="D18" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E18" s="9" t="n">
         <v>5</v>
       </c>
@@ -5917,7 +6305,9 @@
       <c r="C19" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D19" s="9" t="n"/>
+      <c r="D19" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E19" s="9" t="n">
         <v>10</v>
       </c>
@@ -5939,7 +6329,9 @@
       <c r="C20" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D20" s="9" t="n"/>
+      <c r="D20" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E20" s="9" t="n">
         <v>7</v>
       </c>
@@ -5961,7 +6353,9 @@
       <c r="C21" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D21" s="9" t="n"/>
+      <c r="D21" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E21" s="9" t="n">
         <v>5</v>
       </c>
@@ -5983,7 +6377,9 @@
       <c r="C22" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D22" s="9" t="n"/>
+      <c r="D22" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E22" s="9" t="n">
         <v>5</v>
       </c>
@@ -6005,7 +6401,9 @@
       <c r="C23" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D23" s="9" t="n"/>
+      <c r="D23" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E23" s="9" t="n">
         <v>6</v>
       </c>
@@ -6027,7 +6425,9 @@
       <c r="C24" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D24" s="9" t="n"/>
+      <c r="D24" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E24" s="9" t="n">
         <v>5</v>
       </c>
@@ -6049,7 +6449,9 @@
       <c r="C25" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D25" s="9" t="n"/>
+      <c r="D25" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E25" s="9" t="n">
         <v>4</v>
       </c>
@@ -6071,7 +6473,9 @@
       <c r="C26" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D26" s="9" t="n"/>
+      <c r="D26" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E26" s="9" t="n">
         <v>6</v>
       </c>
@@ -6093,7 +6497,9 @@
       <c r="C27" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D27" s="9" t="n"/>
+      <c r="D27" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E27" s="9" t="n">
         <v>7</v>
       </c>
@@ -6115,7 +6521,9 @@
       <c r="C28" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D28" s="9" t="n"/>
+      <c r="D28" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E28" s="9" t="n">
         <v>6</v>
       </c>
@@ -6137,7 +6545,9 @@
       <c r="C29" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D29" s="9" t="n"/>
+      <c r="D29" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E29" s="9" t="n">
         <v>4</v>
       </c>
@@ -6159,7 +6569,9 @@
       <c r="C30" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D30" s="9" t="n"/>
+      <c r="D30" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E30" s="9" t="n">
         <v>6</v>
       </c>
@@ -6228,9 +6640,9 @@
   </sheetData>
   <mergeCells count="8">
     <mergeCell ref="A13:G13"/>
+    <mergeCell ref="A34:E34"/>
+    <mergeCell ref="C7:G7"/>
     <mergeCell ref="A33:G33"/>
-    <mergeCell ref="C7:G7"/>
-    <mergeCell ref="A34:E34"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A31:D31"/>
     <mergeCell ref="A32:E32"/>

--- a/lab-standards/DTE-lab-standard.xlsx
+++ b/lab-standards/DTE-lab-standard.xlsx
@@ -1379,7 +1379,7 @@
         <v>0</v>
       </c>
       <c r="E21" s="9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F21" s="9">
         <f>IFERROR(MIN(C21,D21)*E21/C21,0)</f>
@@ -1403,7 +1403,7 @@
         <v>0</v>
       </c>
       <c r="E22" s="9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F22" s="9">
         <f>IFERROR(MIN(C22,D22)*E22/C22,0)</f>
@@ -1451,7 +1451,7 @@
         <v>0</v>
       </c>
       <c r="E24" s="9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F24" s="9">
         <f>IFERROR(MIN(C24,D24)*E24/C24,0)</f>
@@ -1643,7 +1643,7 @@
         <v>0</v>
       </c>
       <c r="E32" s="9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F32" s="9">
         <f>IFERROR(MIN(C32,D32)*E32/C32,0)</f>
@@ -1715,7 +1715,7 @@
         <v>0</v>
       </c>
       <c r="E35" s="9" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F35" s="9">
         <f>IFERROR(MIN(C35,D35)*E35/C35,0)</f>
@@ -1763,7 +1763,7 @@
         <v>0</v>
       </c>
       <c r="E37" s="9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F37" s="9">
         <f>IFERROR(MIN(C37,D37)*E37/C37,0)</f>
@@ -3154,7 +3154,7 @@
         <v>0</v>
       </c>
       <c r="E19" s="9" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F19" s="9">
         <f>IFERROR(MIN(C19,D19)*E19/C19,0)</f>
@@ -3226,7 +3226,7 @@
         <v>0</v>
       </c>
       <c r="E22" s="9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F22" s="9">
         <f>IFERROR(MIN(C22,D22)*E22/C22,0)</f>
@@ -3250,7 +3250,7 @@
         <v>0</v>
       </c>
       <c r="E23" s="9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F23" s="9">
         <f>IFERROR(MIN(C23,D23)*E23/C23,0)</f>
@@ -3274,7 +3274,7 @@
         <v>0</v>
       </c>
       <c r="E24" s="9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F24" s="9">
         <f>IFERROR(MIN(C24,D24)*E24/C24,0)</f>
@@ -3322,7 +3322,7 @@
         <v>0</v>
       </c>
       <c r="E26" s="9" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F26" s="9">
         <f>IFERROR(MIN(C26,D26)*E26/C26,0)</f>
@@ -3681,7 +3681,7 @@
         <v>0</v>
       </c>
       <c r="E18" s="9" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F18" s="9">
         <f>IFERROR(MIN(C18,D18)*E18/C18,0)</f>
@@ -3801,7 +3801,7 @@
         <v>0</v>
       </c>
       <c r="E23" s="9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F23" s="9">
         <f>IFERROR(MIN(C23,D23)*E23/C23,0)</f>
@@ -3849,7 +3849,7 @@
         <v>0</v>
       </c>
       <c r="E25" s="9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F25" s="9">
         <f>IFERROR(MIN(C25,D25)*E25/C25,0)</f>
@@ -3873,7 +3873,7 @@
         <v>0</v>
       </c>
       <c r="E26" s="9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F26" s="9">
         <f>IFERROR(MIN(C26,D26)*E26/C26,0)</f>
@@ -3897,7 +3897,7 @@
         <v>0</v>
       </c>
       <c r="E27" s="9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F27" s="9">
         <f>IFERROR(MIN(C27,D27)*E27/C27,0)</f>
@@ -3921,7 +3921,7 @@
         <v>0</v>
       </c>
       <c r="E28" s="9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F28" s="9">
         <f>IFERROR(MIN(C28,D28)*E28/C28,0)</f>
@@ -3993,7 +3993,7 @@
         <v>0</v>
       </c>
       <c r="E31" s="9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F31" s="9">
         <f>IFERROR(MIN(C31,D31)*E31/C31,0)</f>
@@ -4017,7 +4017,7 @@
         <v>0</v>
       </c>
       <c r="E32" s="9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F32" s="9">
         <f>IFERROR(MIN(C32,D32)*E32/C32,0)</f>
@@ -4065,7 +4065,7 @@
         <v>0</v>
       </c>
       <c r="E34" s="9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F34" s="9">
         <f>IFERROR(MIN(C34,D34)*E34/C34,0)</f>
@@ -4089,7 +4089,7 @@
         <v>0</v>
       </c>
       <c r="E35" s="9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F35" s="9">
         <f>IFERROR(MIN(C35,D35)*E35/C35,0)</f>
@@ -4137,7 +4137,7 @@
         <v>0</v>
       </c>
       <c r="E37" s="9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F37" s="9">
         <f>IFERROR(MIN(C37,D37)*E37/C37,0)</f>
